--- a/medford_lor_irrigatory.xlsx
+++ b/medford_lor_irrigatory.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР ирригаторы для оснащения клиник и медицинских учреждений. В каталоге представлено 1 позиций.</t>
+          <t>ЛОР ирригаторы для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lor_irrigatory.xlsx
+++ b/medford_lor_irrigatory.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лОР ирригаторы для клиники?</t>
+          <t>Для чего нужен ЛОР-ирригатор?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Полная потребляемая мощность, ВА, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>ЛОР-ирригатор подаёт жидкость под давлением для промывания ушей, носа, околоносовых пазух и лакун миндалин. В кабинете его применяют для удаления серных пробок, санации полости носа и промывания миндалин. Профессиональные модели обеспечивают контролируемую подачу потока. Показания к конкретной процедуре и её допустимость для пациента определяет врач.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем профессиональный ирригатор отличается от бытового?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Профессиональные аппараты рассчитаны на клиническую нагрузку, дают стабильную подачу потока и часто работают в связке с другим ЛОР-оборудованием. Бытовые устройства проще, предназначены для дома и комплектуются мягкими насадками. Для ЛОР-кабинета выбирают профессиональное исполнение с подходящими насадками и режимами под выполняемые процедуры.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как выбрать ирригатор под задачи кабинета?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Отталкиваются от перечня процедур: промывание ушей, носа или миндалин требует разных насадок и режимов подачи. Оценивают стабильность и регулировку потока, комплект сменных частей, удобство дезинфекции и параметры электропитания. Конкретные характеристики сверяют по спецификации модели, а не по общему описанию категории ирригаторов.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какие насадки нужны для промывания?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Насадки подбирают по назначению — отдельно для слухового прохода, полости носа и лакун миндалин. Их наличие в комплекте и доступность для докупки определяют перечень доступных процедур и бесперебойность работы. Совместимость и состав комплекта уточняют у поставщика до покупки, поскольку исполнение отличается у разных аппаратов.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Кому нельзя выполнять промывание?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>У промываний ушей, носа и миндалин есть противопоказания — например, при острых воспалениях или повреждении барабанной перепонки процедуры могут быть недопустимы. Оценку состояния и решение о проведении промывания принимает врач-оториноларинголог. Аппарат — инструмент врача, а не основание для самостоятельного назначения процедуры.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Почему стоматологи не рекомендуют ирригатор?</t>
+          <t>Как обслуживать ЛОР-ирригатор?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Аппарат регулярно дезинфицируют, а насадки обрабатывают или заменяют согласно инструкции производителя. В клинике при высокой частоте применения важны простота очистки и доступность сменных частей. Перечень совместимых дезинфицирующих средств и порядок обработки указывает изготовитель; их соблюдение обеспечивает санитарные требования и ресурс устройства.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Кому нельзя пользоваться ирригатором?</t>
+          <t>Нужно ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да. ЛОР-ирригатор для клинического применения — медицинское изделие, которое вводят в оборот при действующем регистрационном удостоверении Росздравнадзора на модель. Перед приобретением сверяют статус РУ, условия сервисной поддержки и доступность расходных материалов и насадок у поставщика.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР ирригаторы для оснащения клиник и медицинских учреждений.</t>
+          <t>ЛОР-ирригатор — аппарат, который подаёт струю жидкости под давлением для промывания ушей, носа, околоносовых пазух и лакун миндалин. В каталоге представлен профессиональный аппарат для промывания Chammed CMEI-100 южнокорейского производства с полной потребляемой мощностью 310 ВА. Профессиональные ирригаторы применяют в ЛОР-кабинетах для удаления серных пробок, санации носа и промывания миндалин. От бытовых устройств они отличаются стабильной подачей потока и возможностью работы в связке с другим ЛОР-оборудованием.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР ирригаторы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите назначение аппарата</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лОР ирригаторы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала уточняют, для каких процедур нужен ирригатор: промывание слухового прохода и удаление серных пробок, санация носа и пазух или промывание лакун миндалин. От этого зависят требуемые насадки и режимы подачи. Аппарат Chammed CMEI-100 в каталоге отнесён к ушной промывке. Профиль применения определяют по задачам ЛОР-кабинета.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите профессиональное или портативное исполнение</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Профессиональные аппараты рассчитаны на клиническую нагрузку и стабильную подачу потока, часто интегрируются с другим ЛОР-оборудованием. Портативные и бытовые устройства проще и предназначены для домашнего применения с мягкими насадками. Для кабинета выбирают профессиональное исполнение; конкретную модель подбирают под перечень выполняемых процедур.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените управление потоком</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Полная потребляемая мощность, ВА, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Для процедур важна возможность регулировать подачу жидкости, а в ряде аппаратов — температуру и время. Стабильный контролируемый поток снижает дискомфорт пациента. Конкретный набор регулировок сверяют по спецификации выбранной модели, не перенося описания других аппаратов. Параметры подачи согласуют с типом планируемых промываний.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3503,12 +3503,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте комплект насадок</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Насадки различаются по назначению: для ушей, носа или миндалин. Наличие нужных сменных частей и их доступность для докупки определяют, какие процедуры можно выполнять и как долго аппарат прослужит без простоев. Комплектацию и совместимость насадок уточняют у поставщика до приобретения аппарата.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите обработку и гигиену</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>В клинике ирригатор работает с высокой частотой, поэтому важны простота дезинфекции корпуса и обработки или замены насадок. Удобство очистки напрямую влияет на соблюдение санитарных требований и ресурс аппарата. Способ обработки и перечень совместимых средств уточняют по инструкции производителя.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните питание и регистрацию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверяют требования к электропитанию (у Chammed CMEI-100 полная потребляемая мощность 310 ВА) и совместимость с сетью кабинета. Перед вводом в оборот сверяют действующее регистрационное удостоверение Росздравнадзора на модель и условия сервисной поддержки, а также доступность расходных материалов у поставщика.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ЛОР ирригаторы подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на страна производства, полная потребляемая мощность, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Профессиональный ЛОР-ирригатор отличается от бытового прежде всего стабильностью и предсказуемостью потока — от этого зависит и результат, и безопасность процедуры. Выбирают аппарат под задачу: промывание ушей, носа или лакун миндалин требует разных насадок и режимов. Смотрю на удобство дезинфекции и сменные части, поскольку в клинике аппарат работает с высокой нагрузкой. Показания и противопоказания к самой процедуре всегда определяет врач.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3932,13 +3932,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР ирригаторы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ЛОР ирригаторы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-ирригатор подаёт жидкость под давлением для промывания ушей, носа, околоносовых пазух и лакун миндалин. Профессиональные модели, такие как аппарат Chammed CMEI-100 (Южная Корея, полная потребляемая мощность 310 ВА), используют в ЛОР-кабинетах для удаления серных пробок и санации. Их отличают от бытовых ирригаторов стабильная контролируемая подача потока и клиническое исполнение. При выборе оценивают назначение (уши, нос или миндалины), стабильность и регулировку потока, комплект сменных насадок и удобство дезинфекции. Показания и допустимость самой процедуры промывания всегда определяет врач-оториноларинголог.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3975,13 +3975,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое ЛОР-ирригатор</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Полная потребляемая мощность, ВА, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>ЛОР-ирригатор — аппарат, подающий струю жидкости под давлением для промывания ушей, носа, околоносовых пазух и лакун миндалин. В оториноларингологии его используют для удаления серных пробок, санации носа и промывания миндалин. Профессиональные модели дают контролируемую подачу потока и рассчитаны на регулярную клиническую эксплуатацию.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4018,13 +4018,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Виды ирригаторов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Приборы делят на профессиональные и портативные. Профессиональные применяют в клиниках, иногда в составе ЛОР-комбайна, с контролем подачи потока. Портативные и бытовые предназначены для дома и комплектуются мягкими насадками для носа или ушей. Для оснащения кабинета выбирают профессиональное исполнение под конкретный перечень процедур.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4061,13 +4061,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Как выбрать аппарат для промывания</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Выбор начинают с назначения — уши, нос или миндалины, поскольку от этого зависят насадки и режимы. Оценивают стабильность и регулировку потока, комплект сменных частей, удобство дезинфекции и параметры электропитания. В каталоге представлен профессиональный аппарат Chammed CMEI-100 (Южная Корея, 310 ВА) для ушной промывки.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4084,6 +4084,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Эксплуатация и обслуживание</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В клинике ирригатор работает с высокой частотой, поэтому важны простота дезинфекции и доступность сменных насадок. Перед вводом в оборот проверяют регистрационное удостоверение Росздравнадзора, условия сервиса и наличие расходников. Показания и допустимость промывания для конкретного пациента всегда определяет врач-оториноларинголог.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lor_irrigatory</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
